--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9040-2026 artfynd.xlsx
+++ b/artfynd/A 9040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131417887</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
